--- a/samples/migration_report_pcrs.xlsx
+++ b/samples/migration_report_pcrs.xlsx
@@ -62,7 +62,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="M051" sheetId="53" state="visible" r:id="rId53"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Detail'!$A$1:$R$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Detail'!$A$1:$S$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -703,7 +703,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-16 19:53:05</t>
+          <t>2026-07-17 09:27:46</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>samples/pcrs/legacy_vb</t>
+          <t>samples\pcrs\legacy_vb</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>samples/pcrs/new_aspcore</t>
+          <t>samples\pcrs\new_aspcore</t>
         </is>
       </c>
     </row>
@@ -795,7 +795,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>samples/pcrs/method_mapping.csv</t>
+          <t>samples\pcrs\method_mapping.csv</t>
         </is>
       </c>
     </row>
@@ -3342,7 +3342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R52"/>
+  <dimension ref="A1:S52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3362,7 +3362,8 @@
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="55" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3453,6 +3454,11 @@
       </c>
       <c r="R1" s="3" t="inlineStr">
         <is>
+          <t>AI đề xuất giải pháp</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
           <t>Status DEV đánh giá</t>
         </is>
       </c>
@@ -3537,7 +3543,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R2" s="5" t="n"/>
+      <c r="R2" s="12" t="inlineStr"/>
+      <c r="S2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="10" t="n">
@@ -3615,7 +3622,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R3" s="5" t="n"/>
+      <c r="R3" s="12" t="inlineStr"/>
+      <c r="S3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="10" t="n">
@@ -3689,7 +3697,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R4" s="5" t="n"/>
+      <c r="R4" s="12" t="inlineStr"/>
+      <c r="S4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="n">
@@ -3767,7 +3776,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R5" s="5" t="n"/>
+      <c r="R5" s="12" t="inlineStr"/>
+      <c r="S5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="n">
@@ -3845,7 +3855,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R6" s="5" t="n"/>
+      <c r="R6" s="12" t="inlineStr"/>
+      <c r="S6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="n">
@@ -3923,7 +3934,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R7" s="5" t="n"/>
+      <c r="R7" s="12" t="inlineStr"/>
+      <c r="S7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="n">
@@ -4005,7 +4017,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R8" s="5" t="n"/>
+      <c r="R8" s="12" t="inlineStr"/>
+      <c r="S8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="n">
@@ -4083,7 +4096,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R9" s="5" t="n"/>
+      <c r="R9" s="12" t="inlineStr"/>
+      <c r="S9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="n">
@@ -4161,7 +4175,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R10" s="5" t="n"/>
+      <c r="R10" s="12" t="inlineStr"/>
+      <c r="S10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="n">
@@ -4239,7 +4254,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R11" s="5" t="n"/>
+      <c r="R11" s="12" t="inlineStr"/>
+      <c r="S11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="n">
@@ -4317,7 +4333,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R12" s="5" t="n"/>
+      <c r="R12" s="12" t="inlineStr"/>
+      <c r="S12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="n">
@@ -4395,7 +4412,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R13" s="5" t="n"/>
+      <c r="R13" s="12" t="inlineStr"/>
+      <c r="S13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="n">
@@ -4477,7 +4495,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R14" s="5" t="n"/>
+      <c r="R14" s="12" t="inlineStr"/>
+      <c r="S14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="n">
@@ -4555,7 +4574,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R15" s="5" t="n"/>
+      <c r="R15" s="12" t="inlineStr"/>
+      <c r="S15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n">
@@ -4633,7 +4653,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R16" s="5" t="n"/>
+      <c r="R16" s="12" t="inlineStr"/>
+      <c r="S16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="n">
@@ -4715,7 +4736,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R17" s="5" t="n"/>
+      <c r="R17" s="12" t="inlineStr"/>
+      <c r="S17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="n">
@@ -4797,7 +4819,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R18" s="5" t="n"/>
+      <c r="R18" s="12" t="inlineStr"/>
+      <c r="S18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="n">
@@ -4879,7 +4902,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R19" s="5" t="n"/>
+      <c r="R19" s="12" t="inlineStr"/>
+      <c r="S19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="n">
@@ -4957,7 +4981,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R20" s="5" t="n"/>
+      <c r="R20" s="12" t="inlineStr"/>
+      <c r="S20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="n">
@@ -5035,7 +5060,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R21" s="5" t="n"/>
+      <c r="R21" s="12" t="inlineStr"/>
+      <c r="S21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="n">
@@ -5117,7 +5143,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R22" s="5" t="n"/>
+      <c r="R22" s="12" t="inlineStr"/>
+      <c r="S22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="n">
@@ -5195,7 +5222,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R23" s="5" t="n"/>
+      <c r="R23" s="12" t="inlineStr"/>
+      <c r="S23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
@@ -5273,7 +5301,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R24" s="5" t="n"/>
+      <c r="R24" s="12" t="inlineStr"/>
+      <c r="S24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="n">
@@ -5351,7 +5380,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R25" s="5" t="n"/>
+      <c r="R25" s="12" t="inlineStr"/>
+      <c r="S25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
@@ -5433,7 +5463,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R26" s="5" t="n"/>
+      <c r="R26" s="12" t="inlineStr"/>
+      <c r="S26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="n">
@@ -5515,7 +5546,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R27" s="5" t="n"/>
+      <c r="R27" s="12" t="inlineStr"/>
+      <c r="S27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
@@ -5597,7 +5629,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R28" s="5" t="n"/>
+      <c r="R28" s="12" t="inlineStr"/>
+      <c r="S28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="n">
@@ -5679,7 +5712,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R29" s="5" t="n"/>
+      <c r="R29" s="12" t="inlineStr"/>
+      <c r="S29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
@@ -5761,7 +5795,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R30" s="5" t="n"/>
+      <c r="R30" s="12" t="inlineStr"/>
+      <c r="S30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="10" t="n">
@@ -5843,7 +5878,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R31" s="5" t="n"/>
+      <c r="R31" s="12" t="inlineStr"/>
+      <c r="S31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
@@ -5925,7 +5961,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R32" s="5" t="n"/>
+      <c r="R32" s="12" t="inlineStr"/>
+      <c r="S32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="n">
@@ -6007,7 +6044,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R33" s="5" t="n"/>
+      <c r="R33" s="12" t="inlineStr"/>
+      <c r="S33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="10" t="n">
@@ -6089,7 +6127,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R34" s="5" t="n"/>
+      <c r="R34" s="12" t="inlineStr"/>
+      <c r="S34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="10" t="n">
@@ -6171,7 +6210,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R35" s="5" t="n"/>
+      <c r="R35" s="12" t="inlineStr"/>
+      <c r="S35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="10" t="n">
@@ -6253,7 +6293,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R36" s="5" t="n"/>
+      <c r="R36" s="12" t="inlineStr"/>
+      <c r="S36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="10" t="n">
@@ -6335,7 +6376,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R37" s="5" t="n"/>
+      <c r="R37" s="12" t="inlineStr"/>
+      <c r="S37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
@@ -6417,7 +6459,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R38" s="5" t="n"/>
+      <c r="R38" s="12" t="inlineStr"/>
+      <c r="S38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="n">
@@ -6499,7 +6542,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R39" s="5" t="n"/>
+      <c r="R39" s="12" t="inlineStr"/>
+      <c r="S39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="10" t="n">
@@ -6581,7 +6625,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R40" s="5" t="n"/>
+      <c r="R40" s="12" t="inlineStr"/>
+      <c r="S40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="n">
@@ -6663,7 +6708,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R41" s="5" t="n"/>
+      <c r="R41" s="12" t="inlineStr"/>
+      <c r="S41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="10" t="n">
@@ -6745,7 +6791,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R42" s="5" t="n"/>
+      <c r="R42" s="12" t="inlineStr"/>
+      <c r="S42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="10" t="n">
@@ -6823,7 +6870,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R43" s="5" t="n"/>
+      <c r="R43" s="12" t="inlineStr"/>
+      <c r="S43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="10" t="n">
@@ -6905,7 +6953,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R44" s="5" t="n"/>
+      <c r="R44" s="12" t="inlineStr"/>
+      <c r="S44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="n">
@@ -6983,7 +7032,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R45" s="5" t="n"/>
+      <c r="R45" s="12" t="inlineStr"/>
+      <c r="S45" s="5" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="10" t="n">
@@ -7061,7 +7111,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R46" s="5" t="n"/>
+      <c r="R46" s="12" t="inlineStr"/>
+      <c r="S46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="10" t="n">
@@ -7143,7 +7194,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R47" s="5" t="n"/>
+      <c r="R47" s="12" t="inlineStr"/>
+      <c r="S47" s="5" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="10" t="n">
@@ -7221,7 +7273,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R48" s="5" t="n"/>
+      <c r="R48" s="12" t="inlineStr"/>
+      <c r="S48" s="5" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="10" t="n">
@@ -7303,7 +7356,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R49" s="5" t="n"/>
+      <c r="R49" s="12" t="inlineStr"/>
+      <c r="S49" s="5" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="10" t="n">
@@ -7385,7 +7439,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R50" s="5" t="n"/>
+      <c r="R50" s="12" t="inlineStr"/>
+      <c r="S50" s="5" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="n">
@@ -7463,7 +7518,8 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R51" s="5" t="n"/>
+      <c r="R51" s="12" t="inlineStr"/>
+      <c r="S51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="10" t="n">
@@ -7541,11 +7597,12 @@
           <t>AI chưa thực hiện đánh giá</t>
         </is>
       </c>
-      <c r="R52" s="5" t="n"/>
+      <c r="R52" s="12" t="inlineStr"/>
+      <c r="S52" s="5" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R52"/>
-  <conditionalFormatting sqref="R2:R52">
+  <autoFilter ref="A1:S52"/>
+  <conditionalFormatting sqref="S2:S52">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"PASS"</formula>
     </cfRule>
@@ -7563,7 +7620,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="R2:R52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Gia tri khong hop le" error="Chon mot trong: PASS, WARNING, FAIL, MISSING, EXTRA" type="list">
+    <dataValidation sqref="S2:S52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Gia tri khong hop le" error="Chon mot trong: PASS, WARNING, FAIL, MISSING, EXTRA" type="list">
       <formula1>"PASS,WARNING,FAIL,MISSING,EXTRA"</formula1>
     </dataValidation>
   </dataValidations>
